--- a/exports/POLICYBZR_full_report.xlsx
+++ b/exports/POLICYBZR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.21</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>932.55</v>
+        <v>917.2</v>
       </c>
       <c r="I2" t="n">
         <v>929.0121533623357</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>4.08</v>
+        <v>2.37</v>
       </c>
       <c r="L2" t="n">
         <v>4.37</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.07</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.38541666666</v>
+        <v>44593.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>843.05</v>
+        <v>863</v>
       </c>
       <c r="I3" t="n">
         <v>854.3438370617899</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>8.08</v>
+        <v>5.91</v>
       </c>
       <c r="L3" t="n">
         <v>3.35</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>16.74</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44602.55208333334</v>
+        <v>44603.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>873</v>
+        <v>797.85</v>
       </c>
       <c r="I4" t="n">
         <v>826.2389134247928</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K4" t="n">
-        <v>1.16</v>
+        <v>-7.55</v>
       </c>
       <c r="L4" t="n">
-        <v>2.53</v>
+        <v>10.19</v>
       </c>
       <c r="M4" t="n">
-        <v>2.37</v>
+        <v>3.78</v>
       </c>
       <c r="N4" t="n">
-        <v>5.67</v>
+        <v>11.09</v>
       </c>
       <c r="O4" t="n">
         <v>8.390000000000001</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>18.26</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>705</v>
+        <v>732.5</v>
       </c>
       <c r="I5" t="n">
         <v>721.9696711134071</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K5" t="n">
-        <v>11.64</v>
+        <v>8.19</v>
       </c>
       <c r="L5" t="n">
         <v>5.28</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>11.11</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44645.55208333334</v>
+        <v>44648.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>705.3</v>
+        <v>679.1</v>
       </c>
       <c r="I6" t="n">
         <v>679.242292071168</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.71</v>
+        <v>-7.29</v>
       </c>
       <c r="L6" t="n">
-        <v>8.08</v>
+        <v>9.17</v>
       </c>
       <c r="M6" t="n">
         <v>0.07000000000000001</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>11.97</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>730</v>
+        <v>770</v>
       </c>
       <c r="I7" t="n">
         <v>753.7589118883568</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.5</v>
+        <v>-13.39</v>
       </c>
       <c r="L7" t="n">
-        <v>8.15</v>
+        <v>17.07</v>
       </c>
       <c r="M7" t="n">
-        <v>0.93</v>
+        <v>2.05</v>
       </c>
       <c r="N7" t="n">
         <v>5.77</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>10.2</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>749.5</v>
+        <v>705</v>
       </c>
       <c r="I8" t="n">
         <v>736.3274216991181</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.66</v>
+        <v>-8.44</v>
       </c>
       <c r="L8" t="n">
-        <v>3.77</v>
+        <v>8.77</v>
       </c>
       <c r="M8" t="n">
-        <v>0.65</v>
+        <v>1.91</v>
       </c>
       <c r="N8" t="n">
-        <v>6.4</v>
+        <v>6.57</v>
       </c>
       <c r="O8" t="n">
         <v>5.07</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.04</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44694.38541666666</v>
+        <v>44694.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>599.95</v>
+        <v>624</v>
       </c>
       <c r="I9" t="n">
         <v>623.4283281778737</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>14.9</v>
+        <v>11.49</v>
       </c>
       <c r="L9" t="n">
         <v>4.96</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>14.58</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44718.55208333334</v>
+        <v>44719.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>658.5</v>
+        <v>574.55</v>
       </c>
       <c r="I10" t="n">
         <v>616.2921170154216</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>5.53</v>
+        <v>-7.92</v>
       </c>
       <c r="L10" t="n">
-        <v>4.1</v>
+        <v>10.85</v>
       </c>
       <c r="M10" t="n">
         <v>2.86</v>
       </c>
       <c r="N10" t="n">
-        <v>6.92</v>
+        <v>11.88</v>
       </c>
       <c r="O10" t="n">
         <v>13.25</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>19.79</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44774.38541666666</v>
+        <v>44774.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="I11" t="n">
         <v>505.0792562398295</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>55</v>
+        <v>55.16666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>13.5</v>
+        <v>11.93</v>
       </c>
       <c r="L11" t="n">
         <v>11.39</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.25</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44795.55208333334</v>
+        <v>44796.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>524.5</v>
+        <v>520.35</v>
       </c>
       <c r="I12" t="n">
         <v>523.1674861598486</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>3.66</v>
+        <v>2.84</v>
       </c>
       <c r="L12" t="n">
         <v>3.75</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.76</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44816.55208333334</v>
+        <v>44817.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>508</v>
+        <v>543.55</v>
       </c>
       <c r="I13" t="n">
         <v>523.1519479735218</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>2.37</v>
+        <v>-4.46</v>
       </c>
       <c r="L13" t="n">
         <v>6.45</v>
@@ -1182,7 +1337,7 @@
         <v>1.63</v>
       </c>
       <c r="N13" t="n">
-        <v>3.18</v>
+        <v>11.02</v>
       </c>
       <c r="O13" t="n">
         <v>-2.2</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.46</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44825.55208333334</v>
+        <v>44826.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>508.9</v>
+        <v>507</v>
       </c>
       <c r="I14" t="n">
         <v>508.5406244944838</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.37</v>
+        <v>-6.72</v>
       </c>
       <c r="L14" t="n">
         <v>7.19</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.27</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44883.55208333334</v>
+        <v>44886.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>401.55</v>
+        <v>411.2</v>
       </c>
       <c r="I15" t="n">
         <v>407.859694273833</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K15" t="n">
-        <v>20.8</v>
+        <v>18.9</v>
       </c>
       <c r="L15" t="n">
         <v>2.52</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>14.18</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>451.1</v>
+        <v>439.35</v>
       </c>
       <c r="I16" t="n">
         <v>444.2105775263635</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K16" t="n">
-        <v>9.699999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="L16" t="n">
         <v>4.91</v>
       </c>
       <c r="M16" t="n">
-        <v>1.51</v>
+        <v>1.94</v>
       </c>
       <c r="N16" t="n">
         <v>4.19</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>13.13</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44960.55208333334</v>
+        <v>44963.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>427</v>
+        <v>441.5</v>
       </c>
       <c r="I17" t="n">
         <v>436.0437573960664</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K17" t="n">
-        <v>2.81</v>
+        <v>-0.49</v>
       </c>
       <c r="L17" t="n">
         <v>8.57</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.41</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45028.55208333334</v>
+        <v>45029.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>591.5</v>
+        <v>581.45</v>
       </c>
       <c r="I18" t="n">
         <v>585.7536230097637</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>66</v>
       </c>
       <c r="K18" t="n">
-        <v>33.98</v>
+        <v>31.7</v>
       </c>
       <c r="L18" t="n">
         <v>3.73</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45051.55208333334</v>
+        <v>45054.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>594.5</v>
+        <v>615.9</v>
       </c>
       <c r="I19" t="n">
         <v>609.3546457278237</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.24</v>
+        <v>-5.92</v>
       </c>
       <c r="L19" t="n">
-        <v>5.74</v>
+        <v>6.23</v>
       </c>
       <c r="M19" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="N19" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>-1.27</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.99</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45079.38541666666</v>
+        <v>45079.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>597.2</v>
+        <v>589.9</v>
       </c>
       <c r="I20" t="n">
         <v>592.8938265317888</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.04</v>
+        <v>-4.22</v>
       </c>
       <c r="L20" t="n">
-        <v>4.03</v>
+        <v>4.51</v>
       </c>
       <c r="M20" t="n">
         <v>2.56</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>6.16</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45083.55208333334</v>
+        <v>45084.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>624</v>
+        <v>647</v>
       </c>
       <c r="I21" t="n">
         <v>626.2565769504557</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.78</v>
+        <v>-9.68</v>
       </c>
       <c r="L21" t="n">
-        <v>6.54</v>
+        <v>12.86</v>
       </c>
       <c r="M21" t="n">
-        <v>0.53</v>
+        <v>1.33</v>
       </c>
       <c r="N21" t="n">
         <v>4.35</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.93</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45132.38541666666</v>
+        <v>45132.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>739.95</v>
+        <v>715</v>
       </c>
       <c r="I22" t="n">
         <v>721.7932648018613</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>14.37</v>
+        <v>10.51</v>
       </c>
       <c r="L22" t="n">
         <v>6.38</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45139.38541666666</v>
+        <v>45139.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>757.35</v>
+        <v>762.7</v>
       </c>
       <c r="I23" t="n">
         <v>759.3536652990608</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.92</v>
+        <v>-6.67</v>
       </c>
       <c r="L23" t="n">
-        <v>6.92</v>
+        <v>7.41</v>
       </c>
       <c r="M23" t="n">
         <v>1.13</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.08</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45148.55208333334</v>
+        <v>45149.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>732.25</v>
+        <v>723.05</v>
       </c>
       <c r="I24" t="n">
         <v>727.3491579095204</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.99</v>
+        <v>-5.2</v>
       </c>
       <c r="L24" t="n">
         <v>6.36</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>11.7</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45167.55208333334</v>
+        <v>45168.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>758.5</v>
+        <v>772.3</v>
       </c>
       <c r="I25" t="n">
         <v>771.7402266178608</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.9</v>
+        <v>-6.81</v>
       </c>
       <c r="L25" t="n">
-        <v>6.86</v>
+        <v>7.53</v>
       </c>
       <c r="M25" t="n">
         <v>1.32</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>6.69</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45191.38541666666</v>
+        <v>45191.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>759.45</v>
+        <v>749</v>
       </c>
       <c r="I26" t="n">
         <v>749.9092260409824</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.66</v>
+        <v>-3.02</v>
       </c>
       <c r="L26" t="n">
-        <v>3.01</v>
+        <v>3.4</v>
       </c>
       <c r="M26" t="n">
         <v>1.43</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45238.55208333334</v>
+        <v>45239.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>725.05</v>
+        <v>733</v>
       </c>
       <c r="I27" t="n">
         <v>731.5207079674076</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="L27" t="n">
         <v>4.07</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.6</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45271.55208333334</v>
+        <v>45272.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>802</v>
+        <v>795.7</v>
       </c>
       <c r="I28" t="n">
         <v>800.1947801313429</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K28" t="n">
-        <v>9.41</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L28" t="n">
         <v>1.77</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.33</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45301.55208333334</v>
+        <v>45302.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>826.1</v>
+        <v>836.1</v>
       </c>
       <c r="I29" t="n">
         <v>835.6761493544</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.82</v>
+        <v>-5.08</v>
       </c>
       <c r="L29" t="n">
         <v>7.43</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>6.8</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1264.85</v>
+        <v>1226.95</v>
       </c>
       <c r="I30" t="n">
         <v>1242.883038042218</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>92.16666666666667</v>
+        <v>95</v>
       </c>
       <c r="K30" t="n">
-        <v>51.28</v>
+        <v>46.75</v>
       </c>
       <c r="L30" t="n">
         <v>1.36</v>
       </c>
       <c r="M30" t="n">
-        <v>1.5</v>
+        <v>4.26</v>
       </c>
       <c r="N30" t="n">
         <v>7.08</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>11.03</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45412.55208333334</v>
+        <v>45414.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1261.3</v>
+        <v>1303.4</v>
       </c>
       <c r="I31" t="n">
         <v>1290.479587887251</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.8</v>
+        <v>-6.23</v>
       </c>
       <c r="L31" t="n">
-        <v>4.16</v>
+        <v>7.42</v>
       </c>
       <c r="M31" t="n">
         <v>1.82</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45439.55208333334</v>
+        <v>45440.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1251.05</v>
+        <v>1209.7</v>
       </c>
       <c r="I32" t="n">
         <v>1223.368796827819</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.02</v>
+        <v>-7.19</v>
       </c>
       <c r="L32" t="n">
         <v>11.07</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.21</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1266.65</v>
+        <v>1304.65</v>
       </c>
       <c r="I33" t="n">
         <v>1280.786198821173</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.71</v>
+        <v>-7.85</v>
       </c>
       <c r="L33" t="n">
         <v>11.18</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.79</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45559.55208333334</v>
+        <v>45560.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1845</v>
+        <v>1745.2</v>
       </c>
       <c r="I34" t="n">
         <v>1760.90846430599</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>113.1666666666667</v>
+        <v>114</v>
       </c>
       <c r="K34" t="n">
-        <v>41.42</v>
+        <v>33.77</v>
       </c>
       <c r="L34" t="n">
         <v>8.550000000000001</v>
@@ -2379,7 +2786,7 @@
         <v>1.52</v>
       </c>
       <c r="N34" t="n">
-        <v>3.68</v>
+        <v>6.08</v>
       </c>
       <c r="O34" t="n">
         <v>0.93</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.65</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1745</v>
+        <v>1793.05</v>
       </c>
       <c r="I35" t="n">
         <v>1755.397526335035</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K35" t="n">
-        <v>0.01</v>
+        <v>-2.74</v>
       </c>
       <c r="L35" t="n">
         <v>4.86</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.14</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>2076.9</v>
+        <v>1980</v>
       </c>
       <c r="I36" t="n">
         <v>2061.580785595133</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K36" t="n">
-        <v>15.83</v>
+        <v>10.43</v>
       </c>
       <c r="L36" t="n">
         <v>4.5</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>12.1</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1450.85</v>
+        <v>1547.15</v>
       </c>
       <c r="I37" t="n">
         <v>1476.803020891546</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K37" t="n">
-        <v>26.72</v>
+        <v>21.86</v>
       </c>
       <c r="L37" t="n">
         <v>5.3</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.34</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45748.38541666666</v>
+        <v>45748.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>1517.1</v>
+        <v>1515.05</v>
       </c>
       <c r="I38" t="n">
         <v>1516.832318404679</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.94</v>
+        <v>-2.07</v>
       </c>
       <c r="L38" t="n">
         <v>6.21</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.18</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1534.95</v>
+        <v>1602.4</v>
       </c>
       <c r="I39" t="n">
         <v>1595.934853131656</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.31</v>
+        <v>-5.77</v>
       </c>
       <c r="L39" t="n">
-        <v>5.72</v>
+        <v>5.87</v>
       </c>
       <c r="M39" t="n">
         <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>4.62</v>
+        <v>5.8</v>
       </c>
       <c r="O39" t="n">
         <v>-4.77</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.67</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45796.55208333334</v>
+        <v>45797.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1697</v>
+        <v>1648.5</v>
       </c>
       <c r="I40" t="n">
         <v>1664.555547930295</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K40" t="n">
-        <v>5.9</v>
+        <v>2.88</v>
       </c>
       <c r="L40" t="n">
         <v>3.48</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>10.44</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45800.55208333334</v>
+        <v>45803.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1773.3</v>
+        <v>1802.3</v>
       </c>
       <c r="I41" t="n">
         <v>1790.52995150264</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.57</v>
+        <v>-9.33</v>
       </c>
       <c r="L41" t="n">
-        <v>8.52</v>
+        <v>9.67</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="N41" t="n">
         <v>4.27</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45833.55208333334</v>
+        <v>45834.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1838.9</v>
+        <v>1809.3</v>
       </c>
       <c r="I42" t="n">
         <v>1827.206588442237</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K42" t="n">
-        <v>2.03</v>
+        <v>0.39</v>
       </c>
       <c r="L42" t="n">
         <v>4.3</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.01</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45880.38541666666</v>
+        <v>45880.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1832.7</v>
+        <v>1866</v>
       </c>
       <c r="I43" t="n">
         <v>1842.316591661164</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.29</v>
+        <v>-3.13</v>
       </c>
       <c r="L43" t="n">
         <v>4.35</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>7.12</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1814.6</v>
+        <v>1803</v>
       </c>
       <c r="I44" t="n">
         <v>1806.944093435666</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.75</v>
+        <v>-3.38</v>
       </c>
       <c r="L44" t="n">
-        <v>3.21</v>
+        <v>3.69</v>
       </c>
       <c r="M44" t="n">
         <v>0.16</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.95</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45954.55208333334</v>
+        <v>45957.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1681.8</v>
+        <v>1734.4</v>
       </c>
       <c r="I45" t="n">
         <v>1731.948042897605</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>57</v>
+        <v>59.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>6.72</v>
+        <v>3.8</v>
       </c>
       <c r="L45" t="n">
         <v>9.48</v>
@@ -3006,7 +3545,7 @@
         <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>2.5</v>
+        <v>4.06</v>
       </c>
       <c r="O45" t="n">
         <v>-1.85</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.14</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46006.55208333334</v>
+        <v>46007.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1923.7</v>
+        <v>1841.3</v>
       </c>
       <c r="I46" t="n">
         <v>1841.374758106323</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K46" t="n">
-        <v>10.91</v>
+        <v>6.16</v>
       </c>
       <c r="L46" t="n">
         <v>3.08</v>
@@ -3063,7 +3614,7 @@
         <v>1.41</v>
       </c>
       <c r="N46" t="n">
-        <v>3.64</v>
+        <v>5.13</v>
       </c>
       <c r="O46" t="n">
         <v>4.06</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.68</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46013.55208333334</v>
+        <v>46014.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1878</v>
+        <v>1919.8</v>
       </c>
       <c r="I47" t="n">
         <v>1897.783194981552</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.99</v>
+        <v>-4.26</v>
       </c>
       <c r="L47" t="n">
         <v>4.62</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7.2</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46023.38541666666</v>
+        <v>46023.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>1832.2</v>
+        <v>1804.5</v>
       </c>
       <c r="I48" t="n">
         <v>1819.795292761463</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.56</v>
+        <v>-6.01</v>
       </c>
       <c r="L48" t="n">
-        <v>5.72</v>
+        <v>6.27</v>
       </c>
       <c r="M48" t="n">
         <v>0.52</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.97</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46044.38541666666</v>
+        <v>46044.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>1694.1</v>
+        <v>1716.8</v>
       </c>
       <c r="I49" t="n">
         <v>1704.33280540457</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>6.12</v>
+        <v>4.86</v>
       </c>
       <c r="L49" t="n">
         <v>1.6</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>6.37</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46054.55208333334</v>
+        <v>46055.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1625</v>
+        <v>1570.6</v>
       </c>
       <c r="I50" t="n">
         <v>1607.410811117522</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-5.35</v>
+        <v>-8.52</v>
       </c>
       <c r="L50" t="n">
-        <v>7.88</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="M50" t="n">
         <v>0.86</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.26</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46098.55208333334</v>
+        <v>46099.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1498</v>
+        <v>1527.5</v>
       </c>
       <c r="I51" t="n">
         <v>1514.961179605978</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K51" t="n">
-        <v>4.62</v>
+        <v>2.74</v>
       </c>
       <c r="L51" t="n">
         <v>3.46</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.19</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1504</v>
+        <v>1435.6</v>
       </c>
       <c r="I52" t="n">
         <v>1447.0526008458</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.54</v>
+        <v>-6.02</v>
       </c>
       <c r="L52" t="n">
-        <v>4.6</v>
+        <v>6.34</v>
       </c>
       <c r="M52" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="N52" t="n">
-        <v>2.42</v>
+        <v>4.32</v>
       </c>
       <c r="O52" t="n">
         <v>2</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>8.84</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46128.38541666666</v>
+        <v>46128.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1505.4</v>
+        <v>1560</v>
       </c>
       <c r="I53" t="n">
         <v>1522.87653604681</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.86</v>
+        <v>-8.67</v>
       </c>
       <c r="L53" t="n">
-        <v>6.44</v>
+        <v>8.94</v>
       </c>
       <c r="M53" t="n">
         <v>3.12</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1616.1</v>
+        <v>1596</v>
       </c>
       <c r="I54" t="n">
         <v>1596.044605978635</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K54" t="n">
-        <v>3.6</v>
+        <v>2.31</v>
       </c>
       <c r="L54" t="n">
         <v>3.65</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.69</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46160.38541666666</v>
+        <v>46160.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>1718.9</v>
+        <v>1749</v>
       </c>
       <c r="I55" t="n">
         <v>1734.740559982328</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>-7.7</v>
+        <v>-9.59</v>
       </c>
       <c r="L55" t="n">
-        <v>8.02</v>
+        <v>9.82</v>
       </c>
       <c r="M55" t="n">
         <v>1.35</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>7.68</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1716</v>
+        <v>1663.1</v>
       </c>
       <c r="I56" t="n">
         <v>1700.063923733381</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.89</v>
+        <v>-4.91</v>
       </c>
       <c r="L56" t="n">
-        <v>3.19</v>
+        <v>5</v>
       </c>
       <c r="M56" t="n">
         <v>1.06</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.17</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46189.55208333334</v>
+        <v>46190.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1590.8</v>
+        <v>1611.9</v>
       </c>
       <c r="I57" t="n">
         <v>1607.822152312797</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K57" t="n">
-        <v>4.35</v>
+        <v>3.08</v>
       </c>
       <c r="L57" t="n">
         <v>2.75</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.7</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1673</v>
+        <v>1589.1</v>
       </c>
       <c r="I58" t="n">
         <v>1589.544607133391</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K58" t="n">
-        <v>3.79</v>
+        <v>-1.41</v>
       </c>
       <c r="L58" t="n">
-        <v>1.51</v>
+        <v>4.12</v>
       </c>
       <c r="M58" t="n">
-        <v>1.03</v>
+        <v>3.17</v>
       </c>
       <c r="N58" t="n">
-        <v>2.29</v>
+        <v>5.2</v>
       </c>
       <c r="O58" t="n">
         <v>1.96</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.65</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1590</v>
+        <v>1605.3</v>
       </c>
       <c r="I59" t="n">
         <v>1593.663122305673</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.06</v>
+        <v>-1.02</v>
       </c>
       <c r="L59" t="n">
         <v>2.07</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>4.65</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46280.38541666666</v>
+        <v>46280.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>1775.6</v>
+        <v>1752</v>
       </c>
       <c r="I60" t="n">
         <v>1762.575374216044</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>10.61</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L60" t="n">
         <v>1.68</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>5.97</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46288.38541666666</v>
+        <v>46288.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>1854</v>
+        <v>1893</v>
       </c>
       <c r="I61" t="n">
         <v>1856.630422288955</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.82</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>5.82</v>
+        <v>8.73</v>
       </c>
       <c r="M61" t="n">
         <v>0.68</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>7.3</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46288.55208333334</v>
+        <v>46289.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1893</v>
+        <v>1320.1</v>
       </c>
       <c r="I62" t="n">
         <v>1754.823316560098</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>-30.26</v>
       </c>
       <c r="L62" t="n">
-        <v>2.07</v>
+        <v>30.26</v>
       </c>
       <c r="M62" t="n">
-        <v>-0</v>
+        <v>10.32</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>34.26</v>
       </c>
       <c r="O62" t="n">
         <v>5.1</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,14 @@
       <c r="Q63" t="n">
         <v>44</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6137,7 +6900,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="6">
@@ -6147,7 +6910,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="7">
@@ -6157,7 +6920,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113.2</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
@@ -6167,7 +6930,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -6177,7 +6940,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42.2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -6187,7 +6950,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="11">
@@ -6227,7 +6990,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.96</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -6237,7 +7000,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.93</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="16">
@@ -6247,7 +7010,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.92</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -6257,7 +7020,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>51.28</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="18">
@@ -6267,7 +7030,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.8</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -6277,7 +7040,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.19</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="20">
@@ -6287,7 +7050,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.62</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="21">
@@ -6297,7 +7060,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.39</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="22">
@@ -6307,7 +7070,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -6317,7 +7080,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -6327,7 +7090,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="25">
@@ -6337,7 +7100,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.99</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="26">
@@ -6347,7 +7110,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.71</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="27">
@@ -6357,7 +7120,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.25</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="28">
@@ -6367,7 +7130,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
